--- a/data_out/country_spreadsheets/Denmark.xlsx
+++ b/data_out/country_spreadsheets/Denmark.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>79.64</v>
       </c>
+      <c r="X2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>109.23</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>150.69</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>203.77</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>120.43</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>137.31</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>79.64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>62.53</v>
       </c>
+      <c r="X3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>135.68</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>217.75</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>131.79</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>80.67</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>62.53</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>39.37</v>
       </c>
+      <c r="X4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>179.97</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>66.27</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>39.37</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>118.51</v>
       </c>
+      <c r="X5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>161.67</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>67.23999999999999</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>176.02</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>87.77</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>77.18000000000001</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>75.41</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>118.51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>50.45</v>
       </c>
+      <c r="X6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>208.83</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>115.19</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>151.67</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>50.45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>36.89</v>
       </c>
+      <c r="X7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>186.95</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>170.53</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>135.58</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>36.89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>25.08</v>
       </c>
+      <c r="X8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>174.27</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>25.08</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>61.31</v>
       </c>
+      <c r="X9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>60.38</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>201.26</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>61.31</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>47.18</v>
       </c>
+      <c r="X10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>92.88</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>67.39</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>50.28</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>182.46</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>115.45</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55.39</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>47.18</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>59.05</v>
       </c>
+      <c r="X11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>62.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>131.35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>228.25</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>83.39</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>105</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>59.05</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1389,6 +1984,57 @@
         <v>12.82</v>
       </c>
       <c r="W12" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>174.64</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>50.58</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="AN12" t="n">
         <v>85.83</v>
       </c>
     </row>
